--- a/Instructor_Template.xlsx
+++ b/Instructor_Template.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,14 +32,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00333333"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00555555"/>
+      <color rgb="001E3A8A"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +47,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="001a73e8"/>
         <bgColor rgb="001a73e8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+        <bgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF08A"/>
+        <bgColor rgb="00FEF08A"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,11 +88,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -514,31 +523,31 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="25" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Notes on Formatting:</t>
+          <t>⚠️ IMPORTANT FORMATTING NOTES ⚠️</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>- Day: Accepted formats include single days (e.g., 'Friday', 'Saturday') or combined days (e.g., 'Friday/Saturday').</t>
+          <t>- Day: Single days (e.g., 'Friday', 'Saturday') or combined days (e.g., 'Friday/Saturday').</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>- Time: Use standard 12-hour or 24-hour formats (e.g., '09:00 AM', '03:00 PM', '15:00').</t>
+          <t>- Time: Standard 12-hour or 24-hour formats (e.g., '09:00 AM', '03:00 PM', '15:00').</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>- Phone Number: Include the country code (e.g., '+966501234567' or '00966501234567').</t>
+          <t>- Phone Number: MUST include country code (e.g., Egyptian: '+201001234567' or '00201001234567').</t>
         </is>
       </c>
     </row>
